--- a/auxiliary_data/ICD-10_chapter_mapping.xlsx
+++ b/auxiliary_data/ICD-10_chapter_mapping.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20410"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20416"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\meurerst\git\Anon-Lit-Review\eval_rev1\auxiliary_data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\meurerst\git\anonymization-review\auxiliary_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C90E2017-7106-442A-9698-30D34EFF1485}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2715E868-3DD1-4DF9-BA65-39D197D59647}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7092" yWindow="3432" windowWidth="23832" windowHeight="15552" xr2:uid="{5C5B0C05-51CD-4CF5-9CFB-2EAE4098E52C}"/>
   </bookViews>
@@ -30,49 +30,49 @@
     <t>ICD-10 chapter</t>
   </si>
   <si>
-    <t>I) Certain infectious and parasitic diseases</t>
-  </si>
-  <si>
-    <t>II) Neoplasms</t>
-  </si>
-  <si>
-    <t>IV) Endocrine, nutritional and metabolic diseases</t>
-  </si>
-  <si>
-    <t>V) Mental and behavioural disorders</t>
-  </si>
-  <si>
-    <t>VI) Diseases of the nervous system</t>
-  </si>
-  <si>
-    <t>XIV) Diseases of the genitourinary system</t>
-  </si>
-  <si>
-    <t>XIII) Diseases of the musculoskeletal system and connective tissue</t>
-  </si>
-  <si>
-    <t>XII) Diseases of the skin and subcutaneous tissue</t>
-  </si>
-  <si>
-    <t>XI) Diseases of the digestive system</t>
-  </si>
-  <si>
-    <t>X) Diseases of the respiratory system</t>
-  </si>
-  <si>
-    <t>XVIII) Symptoms, signs and abnormal clinical and laboratory findings, not elsewhere classified</t>
-  </si>
-  <si>
-    <t>XXII) Codes for special purposes (COVID-19)</t>
-  </si>
-  <si>
     <t>Name (ICD-10 chapter)</t>
   </si>
   <si>
     <t>other</t>
   </si>
   <si>
-    <t>IX) Diseases of the circulatory system</t>
+    <t>Certain infectious and parasitic diseases</t>
+  </si>
+  <si>
+    <t>Neoplasms</t>
+  </si>
+  <si>
+    <t>Endocrine, nutritional and metabolic diseases</t>
+  </si>
+  <si>
+    <t>Mental and behavioural disorders</t>
+  </si>
+  <si>
+    <t>Diseases of the nervous system</t>
+  </si>
+  <si>
+    <t>Diseases of the circulatory system</t>
+  </si>
+  <si>
+    <t>Diseases of the respiratory system</t>
+  </si>
+  <si>
+    <t>Diseases of the digestive system</t>
+  </si>
+  <si>
+    <t>Diseases of the skin and subcutaneous tissue</t>
+  </si>
+  <si>
+    <t>Diseases of the musculoskeletal system and connective tissue</t>
+  </si>
+  <si>
+    <t>Diseases of the genitourinary system</t>
+  </si>
+  <si>
+    <t>Symptoms, signs and abnormal clinical and laboratory findings, not elsewhere classified</t>
+  </si>
+  <si>
+    <t>Codes for special purposes (COVID-19)</t>
   </si>
 </sst>
 </file>
@@ -432,7 +432,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -440,7 +440,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -448,7 +448,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -456,7 +456,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -464,7 +464,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
@@ -472,7 +472,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
@@ -480,7 +480,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -488,7 +488,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
@@ -496,7 +496,7 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
@@ -504,7 +504,7 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
@@ -512,7 +512,7 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
@@ -520,7 +520,7 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
@@ -528,7 +528,7 @@
         <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
@@ -536,15 +536,15 @@
         <v>22</v>
       </c>
       <c r="B14" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B15" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
